--- a/template/invoice_template.xlsx
+++ b/template/invoice_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\04_Python×GPT\Projects\training\05_invoice_generator\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3830E7D-4CC7-4E38-960F-3625D8B955EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA807CAA-9593-44C1-A329-5ACF831CC12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28020" yWindow="780" windowWidth="12735" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15090" yWindow="2580" windowWidth="12735" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -1013,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:G42"/>
+  <dimension ref="A2:F42"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
@@ -1022,10 +1022,9 @@
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="8.625" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="6.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="42" t="s">
         <v>19</v>
       </c>
@@ -1034,23 +1033,21 @@
       <c r="D2" s="42"/>
       <c r="E2" s="42"/>
       <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-    </row>
-    <row r="3" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="3" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:6" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
       <c r="B4" s="39"/>
       <c r="C4" s="23"/>
     </row>
-    <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="E5" t="s">
         <v>12</v>
@@ -1059,40 +1056,40 @@
         <v>45817</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="E6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="E7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="F9" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="F10" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="F11" s="15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="38" t="s">
         <v>11</v>
       </c>
@@ -1102,10 +1099,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
       <c r="F13" s="16"/>
     </row>
-    <row r="14" spans="1:7" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>6</v>
       </c>
@@ -1125,7 +1122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A15" s="9"/>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -1133,7 +1130,7 @@
       <c r="E15" s="25"/>
       <c r="F15" s="11"/>
     </row>
-    <row r="16" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1325,7 +1322,7 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="E36:F36"/>
@@ -1336,6 +1333,6 @@
     <hyperlink ref="F11" r:id="rId1" display="tel:12-3456-7890" xr:uid="{1183B4A3-6261-435E-BE61-AA65E792ED56}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>